--- a/P13_annexes_completes.xlsx
+++ b/P13_annexes_completes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Projet_13\Khalid318.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C8AB87C-6C57-472F-B72C-14A130FF5FA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08E4FF45-2B57-4480-861E-E9D66B2F6BC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="4" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Cloud" sheetId="1" r:id="rId1"/>
@@ -619,9 +619,6 @@
     <t>Orchestrateur</t>
   </si>
   <si>
-    <t>Serverless, ~0.50$/mois vs 250$/mois pour Airflow</t>
-  </si>
-  <si>
     <t>Monitoring LLM</t>
   </si>
   <si>
@@ -1034,6 +1031,9 @@
   </si>
   <si>
     <t>~365$/mois</t>
+  </si>
+  <si>
+    <t>Serverless, ~0.08$/mois vs 365$/mois pour Airflow</t>
   </si>
 </sst>
 </file>
@@ -1223,11 +1223,11 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -1615,11 +1615,11 @@
       <c r="A12" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1642,41 +1642,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="25" t="s">
+        <v>267</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="26" t="s">
         <v>268</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
-        <v>269</v>
-      </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>271</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>273</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>274</v>
       </c>
       <c r="C5" s="9">
         <v>7</v>
@@ -1688,10 +1688,10 @@
     </row>
     <row r="6" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>275</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>276</v>
       </c>
       <c r="C6" s="16">
         <v>8</v>
@@ -1703,10 +1703,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>277</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>278</v>
       </c>
       <c r="C7" s="9">
         <v>7</v>
@@ -1718,10 +1718,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>279</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>280</v>
       </c>
       <c r="C8" s="16">
         <v>5</v>
@@ -1733,10 +1733,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>281</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>282</v>
       </c>
       <c r="C9" s="9">
         <v>3</v>
@@ -1748,7 +1748,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="18">
@@ -1782,44 +1782,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="25" t="s">
+        <v>283</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="26" t="s">
         <v>284</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
-        <v>285</v>
-      </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>288</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>291</v>
-      </c>
       <c r="C5" s="23" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D5" s="19">
         <v>18</v>
@@ -1827,13 +1827,13 @@
     </row>
     <row r="6" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>293</v>
-      </c>
       <c r="C6" s="24" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D6" s="20">
         <v>10.8</v>
@@ -1844,10 +1844,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D7" s="19">
         <v>0.08</v>
@@ -1855,13 +1855,13 @@
     </row>
     <row r="8" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>296</v>
-      </c>
       <c r="C8" s="24" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D8" s="20">
         <v>0.03</v>
@@ -1869,13 +1869,13 @@
     </row>
     <row r="9" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>298</v>
-      </c>
       <c r="C9" s="23" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D9" s="19">
         <v>0.01</v>
@@ -1886,10 +1886,10 @@
         <v>176</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D10" s="20">
         <v>0.3</v>
@@ -1900,10 +1900,10 @@
         <v>145</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>299</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>300</v>
       </c>
       <c r="D11" s="19">
         <v>0</v>
@@ -1914,10 +1914,10 @@
         <v>119</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D12" s="20">
         <v>0</v>
@@ -1925,7 +1925,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B13" s="17"/>
       <c r="C13" s="17"/>
@@ -1936,47 +1936,47 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="C16" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="C16" s="12" t="s">
-        <v>304</v>
-      </c>
       <c r="D16" s="22" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="B19" s="13" t="s">
         <v>306</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="B20" s="13" t="s">
         <v>308</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
+        <v>309</v>
+      </c>
+      <c r="B21" s="13" t="s">
         <v>310</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -2136,7 +2136,7 @@
         <v>63</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>64</v>
@@ -2177,12 +2177,12 @@
       <c r="A14" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="25"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2303,11 +2303,11 @@
       <c r="A11" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2373,7 +2373,7 @@
         <v>101</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>102</v>
@@ -2448,12 +2448,12 @@
       <c r="A11" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="27" t="s">
         <v>117</v>
       </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2602,11 +2602,11 @@
       <c r="A13" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="27" t="s">
         <v>143</v>
       </c>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2713,11 +2713,11 @@
       <c r="A10" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="27" t="s">
         <v>160</v>
       </c>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2824,11 +2824,11 @@
       <c r="A10" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2850,11 +2850,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -2908,40 +2908,40 @@
         <v>14</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>191</v>
+        <v>329</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>142</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>145</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>176</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -2968,466 +2968,466 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
+      <c r="A1" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>204</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="D4" s="9" t="s">
         <v>208</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>209</v>
       </c>
       <c r="E4" s="9">
         <v>5</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C5" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>213</v>
       </c>
       <c r="E5" s="9">
         <v>2</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="C6" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>215</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>216</v>
       </c>
       <c r="E6" s="9">
         <v>3</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>219</v>
-      </c>
       <c r="C7" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>208</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>209</v>
       </c>
       <c r="E7" s="9">
         <v>5</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>221</v>
-      </c>
       <c r="C8" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E8" s="9">
         <v>2</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>224</v>
-      </c>
       <c r="C9" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E9" s="9">
         <v>2</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>226</v>
-      </c>
       <c r="C10" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E10" s="9">
         <v>2</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>229</v>
-      </c>
       <c r="C11" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E11" s="9">
         <v>1</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>232</v>
-      </c>
       <c r="C12" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E12" s="9">
         <v>1</v>
       </c>
       <c r="F12" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>233</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>236</v>
-      </c>
       <c r="C13" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E13" s="9">
         <v>2</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="C14" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>240</v>
-      </c>
       <c r="D14" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E14" s="9">
         <v>5</v>
       </c>
       <c r="F14" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>241</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>244</v>
-      </c>
       <c r="C15" s="10" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E15" s="9">
         <v>3</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>247</v>
-      </c>
       <c r="C16" s="10" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E16" s="9">
         <v>5</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>250</v>
-      </c>
       <c r="C17" s="10" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E17" s="9">
         <v>3</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="C18" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="D18" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="G18" s="4" t="s">
         <v>254</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="C19" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>257</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="C20" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="G20" s="4" t="s">
         <v>260</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B23" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>263</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B24" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="C24" s="14" t="s">
         <v>265</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
